--- a/main/StructureDefinition-bc-note-extension.xlsx
+++ b/main/StructureDefinition-bc-note-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-30T21:39:06+00:00</t>
+    <t>2026-04-01T23:28:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1261,7 +1261,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>99</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>114</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>121</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>126</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>127</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>132</v>
       </c>
@@ -2509,7 +2509,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>137</v>
       </c>
@@ -2824,12 +2824,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK19">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
